--- a/public/sample_bank_statement.xlsx
+++ b/public/sample_bank_statement.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank Statement" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank Transactions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,212 +434,187 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Bank Account</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Reference Number</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Description</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Reference Number</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Bank Account</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Currency</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>15000.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Automan Operating Account - BDO Unibank, Inc.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Automan Car Care Center</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DEP-2026-001</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Customer Direct Deposit Ref 001</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>DEP-2026-001</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Automan Operating Account - BDO Unibank</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Inc.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PHP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>4500.00</t>
-        </is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4500</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Automan Operating Account - BDO Unibank, Inc.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Automan Car Care Center</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CHQ-2026-002</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Supplier Payment Auto-Debit</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CHQ-2026-002</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Automan Operating Account - BDO Unibank</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Inc.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PHP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>22000.00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Automan Operating Account - BDO Unibank, Inc.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Automan Car Care Center</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DEP-2026-003</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>Check Clearing Collection</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>DEP-2026-003</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Automan Operating Account - BDO Unibank</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Inc.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PHP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1500.00</t>
-        </is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1500</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Automan Operating Account - BDO Unibank, Inc.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Automan Car Care Center</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FEE-2026-004</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>Monthly Bank Maintenance Fee</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>FEE-2026-004</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Automan Operating Account - BDO Unibank</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Inc.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>PHP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>35000.00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Automan Operating Account - BDO Unibank, Inc.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Automan Car Care Center</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DEP-2026-005</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>Corporate Fleet Service Payment</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>DEP-2026-005</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Automan Operating Account - BDO Unibank</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Inc.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PHP</t>
         </is>
       </c>
     </row>
